--- a/outputs/44913.xlsx
+++ b/outputs/44913.xlsx
@@ -152,7 +152,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -174,10 +174,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -464,10 +460,6 @@
       <c r="C2" s="5" t="n">
         <v>44531</v>
       </c>
-      <c r="D2" s="1" t="str">
-        <f aca="false">IF(B2=MAX($B$2:$B$5),B2,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
@@ -479,8 +471,7 @@
       <c r="C3" s="5" t="n">
         <v>44562</v>
       </c>
-      <c r="D3" s="6" t="n">
-        <f aca="false">IF(B3=MAX($B$2:$B$5),B3,"")</f>
+      <c r="D3" s="1" t="n">
         <v>117.17</v>
       </c>
     </row>
@@ -494,10 +485,6 @@
       <c r="C4" s="5" t="n">
         <v>44593</v>
       </c>
-      <c r="D4" s="1" t="str">
-        <f aca="false">IF(B4=MAX($B$2:$B$5),B4,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
@@ -509,10 +496,6 @@
       <c r="C5" s="5" t="n">
         <v>44621</v>
       </c>
-      <c r="D5" s="1" t="str">
-        <f aca="false">IF(B5=MAX($B$2:$B$5),B5,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
@@ -524,10 +507,6 @@
       <c r="C6" s="5" t="n">
         <v>44531</v>
       </c>
-      <c r="D6" s="1" t="str">
-        <f aca="false">IF(B6=MAX($B$6:$B$9),B6,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="n">
@@ -539,10 +518,6 @@
       <c r="C7" s="5" t="n">
         <v>44562</v>
       </c>
-      <c r="D7" s="1" t="str">
-        <f aca="false">IF(B7=MAX($B$6:$B$9),B7,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="n">
@@ -554,8 +529,7 @@
       <c r="C8" s="5" t="n">
         <v>44593</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <f aca="false">IF(B8=MAX($B$6:$B$9),B8,"")</f>
+      <c r="D8" s="1" t="n">
         <v>34.84</v>
       </c>
     </row>
@@ -569,10 +543,6 @@
       <c r="C9" s="5" t="n">
         <v>44621</v>
       </c>
-      <c r="D9" s="1" t="str">
-        <f aca="false">IF(B9=MAX($B$6:$B$9),B9,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="n">
@@ -584,10 +554,6 @@
       <c r="C10" s="5" t="n">
         <v>44531</v>
       </c>
-      <c r="D10" s="1" t="str">
-        <f aca="false">IF(B10=MAX($B$10:$B$13),B10,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="n">
@@ -599,8 +565,7 @@
       <c r="C11" s="5" t="n">
         <v>44562</v>
       </c>
-      <c r="D11" s="6" t="n">
-        <f aca="false">IF(B11=MAX($B$10:$B$13),B11,"")</f>
+      <c r="D11" s="1" t="n">
         <v>30.48</v>
       </c>
     </row>
@@ -614,10 +579,6 @@
       <c r="C12" s="5" t="n">
         <v>44593</v>
       </c>
-      <c r="D12" s="1" t="str">
-        <f aca="false">IF(B12=MAX($B$10:$B$13),B12,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="n">
@@ -628,10 +589,6 @@
       </c>
       <c r="C13" s="5" t="n">
         <v>44621</v>
-      </c>
-      <c r="D13" s="1" t="str">
-        <f aca="false">IF(B13=MAX($B$10:$B$13),B13,"")</f>
-        <v/>
       </c>
     </row>
   </sheetData>
